--- a/WEFENI.xlsx
+++ b/WEFENI.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -459,22 +459,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>120537.4229355702</v>
+        <v>3010.703799999999</v>
       </c>
       <c r="E2" t="n">
-        <v>121128.2483683327</v>
+        <v>3287.181999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>121132.9034404697</v>
+        <v>3563.660199999999</v>
       </c>
       <c r="G2" t="n">
-        <v>121132.914302912</v>
+        <v>3563.660199999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,22 +488,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>39905.72789000626</v>
+        <v>1570978.753679286</v>
       </c>
       <c r="E3" t="n">
-        <v>39905.72789000379</v>
+        <v>1570978.753242223</v>
       </c>
       <c r="F3" t="n">
-        <v>39905.72788999999</v>
+        <v>1570978.753378689</v>
       </c>
       <c r="G3" t="n">
-        <v>39905.72788999999</v>
+        <v>1570978.753158895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -517,22 +517,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39905.72788999999</v>
+        <v>1461387.732366475</v>
       </c>
       <c r="E4" t="n">
-        <v>39905.72788999999</v>
+        <v>1581701.47496347</v>
       </c>
       <c r="F4" t="n">
-        <v>39905.72788999999</v>
+        <v>1583453.766156408</v>
       </c>
       <c r="G4" t="n">
-        <v>39905.72788999999</v>
+        <v>1583455.646879986</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -546,27 +546,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>39905.72788999999</v>
+        <v>1456674.704883361</v>
       </c>
       <c r="E5" t="n">
-        <v>39905.72788999999</v>
+        <v>1120970.287191721</v>
       </c>
       <c r="F5" t="n">
-        <v>39905.72788999999</v>
+        <v>180453.4594476054</v>
       </c>
       <c r="G5" t="n">
-        <v>39905.72788999999</v>
+        <v>180453.4594476054</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DIV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -575,45 +575,74 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>39905.72788999999</v>
+        <v>1224742.465828487</v>
       </c>
       <c r="E6" t="n">
-        <v>39905.72788999999</v>
+        <v>1224725.750110737</v>
       </c>
       <c r="F6" t="n">
-        <v>39905.72788999999</v>
+        <v>1224366.039536898</v>
       </c>
       <c r="G6" t="n">
-        <v>39905.72788999999</v>
+        <v>571149.9232035831</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3563.660225888322</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3563.660226084324</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3563.660226189856</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3563.660227355065</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>MCDA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>ENERGY</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>39905.72788999999</v>
-      </c>
-      <c r="E7" t="n">
-        <v>39905.72788999999</v>
-      </c>
-      <c r="F7" t="n">
-        <v>39905.72788999999</v>
-      </c>
-      <c r="G7" t="n">
-        <v>39905.72788999999</v>
+      <c r="D8" t="n">
+        <v>3563.660199999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3563.660199999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3563.660199999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3563.660199999999</v>
       </c>
     </row>
   </sheetData>
@@ -627,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +698,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>41767.24235980022</v>
+        <v>86.65774616561268</v>
       </c>
       <c r="E2" t="n">
-        <v>43417.99611903779</v>
+        <v>86.65774616561271</v>
       </c>
       <c r="F2" t="n">
-        <v>43506.42540307778</v>
+        <v>86.65774616561271</v>
       </c>
       <c r="G2" t="n">
-        <v>44141.08397593654</v>
+        <v>86.65774616561271</v>
       </c>
     </row>
     <row r="3">
@@ -698,16 +727,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1048.085967043098</v>
+        <v>86.65774616559321</v>
       </c>
       <c r="E3" t="n">
-        <v>1048.085966931793</v>
+        <v>86.6577461655932</v>
       </c>
       <c r="F3" t="n">
-        <v>1042.670248993237</v>
+        <v>86.6577461655932</v>
       </c>
       <c r="G3" t="n">
-        <v>1044.715925189102</v>
+        <v>86.6577461655932</v>
       </c>
     </row>
     <row r="4">
@@ -727,16 +756,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1044.715925189102</v>
+        <v>86.6577461655932</v>
       </c>
       <c r="E4" t="n">
-        <v>1048.085966934655</v>
+        <v>1.690503757746427</v>
       </c>
       <c r="F4" t="n">
-        <v>1048.085966934655</v>
+        <v>1.690503757746427</v>
       </c>
       <c r="G4" t="n">
-        <v>1048.085966934655</v>
+        <v>1.690503757746427</v>
       </c>
     </row>
     <row r="5">
@@ -756,16 +785,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1048.085966934655</v>
+        <v>86.657746165605</v>
       </c>
       <c r="E5" t="n">
-        <v>1041.709924905125</v>
+        <v>86.657746165605</v>
       </c>
       <c r="F5" t="n">
-        <v>1041.709924905125</v>
+        <v>86.657746165605</v>
       </c>
       <c r="G5" t="n">
-        <v>1041.709924905125</v>
+        <v>86.657746165605</v>
       </c>
     </row>
     <row r="6">
@@ -776,7 +805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DIV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -785,16 +814,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1489.085966975521</v>
+        <v>86.657746165605</v>
       </c>
       <c r="E6" t="n">
-        <v>1044.305729965886</v>
+        <v>86.657746165605</v>
       </c>
       <c r="F6" t="n">
-        <v>1042.670251360156</v>
+        <v>86.657746165605</v>
       </c>
       <c r="G6" t="n">
-        <v>1044.721864679174</v>
+        <v>86.657746165605</v>
       </c>
     </row>
     <row r="7">
@@ -805,25 +834,54 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>86.65774616561271</v>
+      </c>
+      <c r="E7" t="n">
+        <v>86.65774616560965</v>
+      </c>
+      <c r="F7" t="n">
+        <v>86.65774616560417</v>
+      </c>
+      <c r="G7" t="n">
+        <v>86.6577461655987</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hh_1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>MCDA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>GHG</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>1041.709924905125</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1045.791181666176</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1047.144518715384</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1047.144518715384</v>
+      <c r="D8" t="n">
+        <v>1.690503757746427</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.69050375774643</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.69050375774643</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.69050375774643</v>
       </c>
     </row>
   </sheetData>
@@ -837,7 +895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -865,7 +923,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -879,22 +937,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>42859.58197307197</v>
+        <v>47297.58905493959</v>
       </c>
       <c r="E2" t="n">
-        <v>42859.58197307197</v>
+        <v>47297.58905493959</v>
       </c>
       <c r="F2" t="n">
-        <v>37029.46224674962</v>
+        <v>43131.30427367289</v>
       </c>
       <c r="G2" t="n">
-        <v>39203.24218526269</v>
+        <v>46130.07071693157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -908,22 +966,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>42859.58197307197</v>
+        <v>23040</v>
       </c>
       <c r="E3" t="n">
-        <v>42859.58197307197</v>
+        <v>23040</v>
       </c>
       <c r="F3" t="n">
-        <v>37029.46224674962</v>
+        <v>23040</v>
       </c>
       <c r="G3" t="n">
-        <v>39203.24218526269</v>
+        <v>23040</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -937,22 +995,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42859.58197307197</v>
+        <v>23040</v>
       </c>
       <c r="E4" t="n">
-        <v>42859.58197307197</v>
+        <v>23040</v>
       </c>
       <c r="F4" t="n">
-        <v>37029.46224674962</v>
+        <v>23040</v>
       </c>
       <c r="G4" t="n">
-        <v>39203.24218526269</v>
+        <v>23040</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,27 +1024,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>42859.58197307197</v>
+        <v>23040</v>
       </c>
       <c r="E5" t="n">
-        <v>42859.58197307197</v>
+        <v>23040</v>
       </c>
       <c r="F5" t="n">
-        <v>37029.46224674962</v>
+        <v>23040</v>
       </c>
       <c r="G5" t="n">
-        <v>39203.24218526269</v>
+        <v>23040</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DIV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -995,45 +1053,74 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>42859.58197307197</v>
+        <v>23040</v>
       </c>
       <c r="E6" t="n">
-        <v>42859.58197307197</v>
+        <v>23040</v>
       </c>
       <c r="F6" t="n">
-        <v>37029.46224674962</v>
+        <v>23040</v>
       </c>
       <c r="G6" t="n">
-        <v>39203.24218526269</v>
+        <v>23040</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>23040</v>
+      </c>
+      <c r="E7" t="n">
+        <v>23040</v>
+      </c>
+      <c r="F7" t="n">
+        <v>23040</v>
+      </c>
+      <c r="G7" t="n">
+        <v>23040</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>MCDA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>water</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>42859.58197307197</v>
-      </c>
-      <c r="E7" t="n">
-        <v>42859.58197307197</v>
-      </c>
-      <c r="F7" t="n">
-        <v>37029.46224674962</v>
-      </c>
-      <c r="G7" t="n">
-        <v>39203.24218526269</v>
+      <c r="D8" t="n">
+        <v>23040</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23040</v>
+      </c>
+      <c r="F8" t="n">
+        <v>23040</v>
+      </c>
+      <c r="G8" t="n">
+        <v>23040</v>
       </c>
     </row>
   </sheetData>
@@ -1047,7 +1134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1089,16 +1176,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14617.51517104317</v>
+        <v>8844.535030510599</v>
       </c>
       <c r="E2" t="n">
-        <v>15803.93802436576</v>
+        <v>8844.535030510599</v>
       </c>
       <c r="F2" t="n">
-        <v>15807.62571916758</v>
+        <v>8844.535030510599</v>
       </c>
       <c r="G2" t="n">
-        <v>15741.58737031025</v>
+        <v>8844.535030510599</v>
       </c>
     </row>
     <row r="3">
@@ -1118,16 +1205,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>250.6680318412663</v>
+        <v>8842.14375273282</v>
       </c>
       <c r="E3" t="n">
-        <v>250.6680318412668</v>
+        <v>8842.14375273282</v>
       </c>
       <c r="F3" t="n">
-        <v>154.8013292546502</v>
+        <v>8842.14375273282</v>
       </c>
       <c r="G3" t="n">
-        <v>154.9014131502542</v>
+        <v>8842.14375273282</v>
       </c>
     </row>
     <row r="4">
@@ -1147,16 +1234,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>154.9014131502542</v>
+        <v>8708.810419399486</v>
       </c>
       <c r="E4" t="n">
-        <v>154.8615804111141</v>
+        <v>8704.312852516152</v>
       </c>
       <c r="F4" t="n">
-        <v>154.8615804111141</v>
+        <v>8704.312852516152</v>
       </c>
       <c r="G4" t="n">
-        <v>154.8615804111141</v>
+        <v>8704.312852516152</v>
       </c>
     </row>
     <row r="5">
@@ -1176,16 +1263,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>154.8615804111141</v>
+        <v>8842.14375273282</v>
       </c>
       <c r="E5" t="n">
-        <v>154.9553241732992</v>
+        <v>8842.14375273282</v>
       </c>
       <c r="F5" t="n">
-        <v>154.9553241732992</v>
+        <v>8842.14375273282</v>
       </c>
       <c r="G5" t="n">
-        <v>154.9553241732992</v>
+        <v>8842.14375273282</v>
       </c>
     </row>
     <row r="6">
@@ -1196,7 +1283,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DIV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1205,16 +1292,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>574.3196449255199</v>
+        <v>8842.14375273282</v>
       </c>
       <c r="E6" t="n">
-        <v>154.8573067931823</v>
+        <v>8842.14375273282</v>
       </c>
       <c r="F6" t="n">
-        <v>154.8013292546502</v>
+        <v>8842.14375273282</v>
       </c>
       <c r="G6" t="n">
-        <v>154.8438307022274</v>
+        <v>8842.14375273282</v>
       </c>
     </row>
     <row r="7">
@@ -1225,25 +1312,54 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8842.14375273282</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8842.14375273282</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8842.14375273282</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8842.14375273282</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hh_1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>MCDA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>income</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>250.7617757862024</v>
-      </c>
-      <c r="E7" t="n">
-        <v>357.1478797752738</v>
-      </c>
-      <c r="F7" t="n">
-        <v>357.1272812139573</v>
-      </c>
-      <c r="G7" t="n">
-        <v>357.1272812139573</v>
+      <c r="D8" t="n">
+        <v>8840.037463627265</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8840.037463627265</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8840.037463627265</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8840.037463627265</v>
       </c>
     </row>
   </sheetData>
@@ -1257,7 +1373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1285,30 +1401,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>WAT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>205490.6850624523</v>
+      </c>
+      <c r="E2" t="n">
+        <v>205490.685189569</v>
+      </c>
+      <c r="F2" t="n">
+        <v>205490.6855142635</v>
+      </c>
+      <c r="G2" t="n">
+        <v>205490.6856176499</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>233141.0465829483</v>
+      </c>
+      <c r="E3" t="n">
+        <v>247539.8570255056</v>
+      </c>
+      <c r="F3" t="n">
+        <v>249787.2259379516</v>
+      </c>
+      <c r="G3" t="n">
+        <v>249787.755707938</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>220159.8280485237</v>
+      </c>
+      <c r="E4" t="n">
+        <v>195994.8033080228</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40584.0883077423</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40584.0883077423</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>182004.7963540292</v>
+      </c>
+      <c r="E5" t="n">
+        <v>182003.4881259331</v>
+      </c>
+      <c r="F5" t="n">
+        <v>181975.3363225936</v>
+      </c>
+      <c r="G5" t="n">
+        <v>100957.2112180278</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.822438565663777e-06</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.918062587310977e-06</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.91841277547557e-06</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.994267382259757e-06</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>hh_1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>productivity</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>25605.45109315393</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27686.64371976296</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27687.02696109384</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27687.09330005233</v>
+      <c r="D7" t="n">
+        <v>19206.23065983087</v>
+      </c>
+      <c r="E7" t="n">
+        <v>20895.01913712193</v>
+      </c>
+      <c r="F7" t="n">
+        <v>20897.31498642389</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20897.31498642392</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hh_1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MCDA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.006998137601535e-06</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.231336364014221e-06</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.154851598203606e-06</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.079514109437754e-06</v>
       </c>
     </row>
   </sheetData>

--- a/WEFENI.xlsx
+++ b/WEFENI.xlsx
@@ -417,23 +417,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="D1" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -459,16 +459,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>120537.4229355702</v>
+        <v>92282.15034589486</v>
       </c>
       <c r="E2" t="n">
-        <v>121128.2483683327</v>
+        <v>92278.43447680972</v>
       </c>
       <c r="F2" t="n">
-        <v>121132.9034404697</v>
+        <v>92278.80610399968</v>
       </c>
       <c r="G2" t="n">
-        <v>121132.914302912</v>
+        <v>3563.660199999999</v>
       </c>
     </row>
     <row r="3">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>39905.72789000626</v>
+        <v>18949.03392651262</v>
       </c>
       <c r="E3" t="n">
-        <v>39905.72789000379</v>
+        <v>18945.54603447114</v>
       </c>
       <c r="F3" t="n">
-        <v>39905.72788999999</v>
+        <v>18944.9535406947</v>
       </c>
       <c r="G3" t="n">
-        <v>39905.72788999999</v>
+        <v>1570978.753158895</v>
       </c>
     </row>
     <row r="4">
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39905.72788999999</v>
+        <v>98991.98572184819</v>
       </c>
       <c r="E4" t="n">
-        <v>39905.72788999999</v>
+        <v>98991.82574852856</v>
       </c>
       <c r="F4" t="n">
-        <v>39905.72788999999</v>
+        <v>98991.82574852856</v>
       </c>
       <c r="G4" t="n">
-        <v>39905.72788999999</v>
+        <v>1583455.646879986</v>
       </c>
     </row>
     <row r="5">
@@ -546,16 +546,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>39905.72788999999</v>
+        <v>18939.15885221006</v>
       </c>
       <c r="E5" t="n">
-        <v>39905.72788999999</v>
+        <v>18939.15885221006</v>
       </c>
       <c r="F5" t="n">
-        <v>39905.72788999999</v>
+        <v>18939.15885221006</v>
       </c>
       <c r="G5" t="n">
-        <v>39905.72788999999</v>
+        <v>180453.4594476054</v>
       </c>
     </row>
     <row r="6">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DIV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -575,16 +575,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>39905.72788999999</v>
+        <v>18947.04819459299</v>
       </c>
       <c r="E6" t="n">
-        <v>39905.72788999999</v>
+        <v>18947.04819459299</v>
       </c>
       <c r="F6" t="n">
-        <v>39905.72788999999</v>
+        <v>18947.04819459299</v>
       </c>
       <c r="G6" t="n">
-        <v>39905.72788999999</v>
+        <v>571149.9232035831</v>
       </c>
     </row>
     <row r="7">
@@ -595,25 +595,236 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>18989.72124165506</v>
+      </c>
+      <c r="E7" t="n">
+        <v>18976.36411548773</v>
+      </c>
+      <c r="F7" t="n">
+        <v>18974.73861815869</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3563.660227355065</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hh_1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>MCDA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>ENERGY</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>39905.72788999999</v>
-      </c>
-      <c r="E7" t="n">
-        <v>39905.72788999999</v>
-      </c>
-      <c r="F7" t="n">
-        <v>39905.72788999999</v>
-      </c>
-      <c r="G7" t="n">
-        <v>39905.72788999999</v>
+      <c r="D8" t="n">
+        <v>37013.33862185591</v>
+      </c>
+      <c r="E8" t="n">
+        <v>37030.29371627104</v>
+      </c>
+      <c r="F8" t="n">
+        <v>36910.30822106841</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3563.660199999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>631967.5967587101</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1170266.555651548</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1178610.683462144</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>WAT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2345.5104701121</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2292.615003721067</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2256.910563907121</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1640316.602233049</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1638113.834028471</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1585886.506705982</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2225.847701268988</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2225.847701268988</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2225.847701268988</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2225.847701268988</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2225.847701268988</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2225.847701268988</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2740.953460798709</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2628.178543691161</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2512.12397630036</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MCDA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>39889.16203681844</v>
+      </c>
+      <c r="E15" t="n">
+        <v>38724.75139094591</v>
+      </c>
+      <c r="F15" t="n">
+        <v>38914.16373466252</v>
       </c>
     </row>
   </sheetData>
@@ -627,23 +838,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="D1" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -655,7 +866,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -669,22 +880,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>41767.24235980022</v>
+        <v>2e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>43417.99611903779</v>
+        <v>2e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>43506.42540307778</v>
+        <v>2e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>44141.08397593654</v>
+        <v>86.65774616561271</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -698,22 +909,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1048.085967043098</v>
+        <v>2e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1048.085966931793</v>
+        <v>2e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1042.670248993237</v>
+        <v>2e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1044.715925189102</v>
+        <v>86.6577461655932</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -727,22 +938,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1044.715925189102</v>
+        <v>2e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1048.085966934655</v>
+        <v>2e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1048.085966934655</v>
+        <v>2e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1048.085966934655</v>
+        <v>1.690503757746427</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -756,27 +967,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1048.085966934655</v>
+        <v>2e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1041.709924905125</v>
+        <v>2e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1041.709924905125</v>
+        <v>2e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1041.709924905125</v>
+        <v>86.657746165605</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DIV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -785,45 +996,256 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1489.085966975521</v>
+        <v>2e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1044.305729965886</v>
+        <v>2e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1042.670251360156</v>
+        <v>2e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1044.721864679174</v>
+        <v>86.657746165605</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="G7" t="n">
+        <v>86.6577461655987</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hh_3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>MCDA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>GHG</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>1041.709924905125</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1045.791181666176</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1047.144518715384</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1047.144518715384</v>
+      <c r="D8" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.69050375774643</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>96875.39640851613</v>
+      </c>
+      <c r="E9" t="n">
+        <v>173374.1043568258</v>
+      </c>
+      <c r="F9" t="n">
+        <v>173990.7858384215</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>WAT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>20564.71573362437</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19969.36025504981</v>
+      </c>
+      <c r="F10" t="n">
+        <v>19567.49530701198</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>412587.4099027446</v>
+      </c>
+      <c r="E11" t="n">
+        <v>474448.4938771146</v>
+      </c>
+      <c r="F11" t="n">
+        <v>501974.9229079931</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>19217.87280221906</v>
+      </c>
+      <c r="E12" t="n">
+        <v>19217.87280221906</v>
+      </c>
+      <c r="F12" t="n">
+        <v>19217.87280221906</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>19217.87280221906</v>
+      </c>
+      <c r="E13" t="n">
+        <v>19217.87280221906</v>
+      </c>
+      <c r="F13" t="n">
+        <v>19217.87280221906</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>23926.24391135458</v>
+      </c>
+      <c r="E14" t="n">
+        <v>22500.07695600611</v>
+      </c>
+      <c r="F14" t="n">
+        <v>21396.87881049765</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MCDA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>29447.87324184592</v>
+      </c>
+      <c r="E15" t="n">
+        <v>30439.96748428605</v>
+      </c>
+      <c r="F15" t="n">
+        <v>21384.99377438569</v>
       </c>
     </row>
   </sheetData>
@@ -837,23 +1259,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="D1" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -865,7 +1287,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -879,22 +1301,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>42859.58197307197</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>42859.58197307197</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>37029.46224674962</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>39203.24218526269</v>
+        <v>46130.07071693157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -908,22 +1330,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>42859.58197307197</v>
+        <v>204081632.6530612</v>
       </c>
       <c r="E3" t="n">
-        <v>42859.58197307197</v>
+        <v>204081632.6530612</v>
       </c>
       <c r="F3" t="n">
-        <v>37029.46224674962</v>
+        <v>204081632.6530612</v>
       </c>
       <c r="G3" t="n">
-        <v>39203.24218526269</v>
+        <v>23040</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -937,22 +1359,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42859.58197307197</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>42859.58197307197</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>37029.46224674962</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>39203.24218526269</v>
+        <v>23040</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,27 +1388,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>42859.58197307197</v>
+        <v>204081632.6530612</v>
       </c>
       <c r="E5" t="n">
-        <v>42859.58197307197</v>
+        <v>204081632.6530612</v>
       </c>
       <c r="F5" t="n">
-        <v>37029.46224674962</v>
+        <v>204081632.6530612</v>
       </c>
       <c r="G5" t="n">
-        <v>39203.24218526269</v>
+        <v>23040</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DIV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -995,45 +1417,256 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>42859.58197307197</v>
+        <v>204081632.6530612</v>
       </c>
       <c r="E6" t="n">
-        <v>42859.58197307197</v>
+        <v>204081632.6530612</v>
       </c>
       <c r="F6" t="n">
-        <v>37029.46224674962</v>
+        <v>204081632.6530612</v>
       </c>
       <c r="G6" t="n">
-        <v>39203.24218526269</v>
+        <v>23040</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>23040</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hh_3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>MCDA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>water</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>42859.58197307197</v>
-      </c>
-      <c r="E7" t="n">
-        <v>42859.58197307197</v>
-      </c>
-      <c r="F7" t="n">
-        <v>37029.46224674962</v>
-      </c>
-      <c r="G7" t="n">
-        <v>39203.24218526269</v>
+      <c r="D8" t="n">
+        <v>204081632.6530612</v>
+      </c>
+      <c r="E8" t="n">
+        <v>204081632.6530612</v>
+      </c>
+      <c r="F8" t="n">
+        <v>204081632.6530612</v>
+      </c>
+      <c r="G8" t="n">
+        <v>23040</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>234711961773.5677</v>
+      </c>
+      <c r="E9" t="n">
+        <v>237319865515.3459</v>
+      </c>
+      <c r="F9" t="n">
+        <v>239666986625.72</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>WAT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>191901627620.6569</v>
+      </c>
+      <c r="E10" t="n">
+        <v>186357827026.7651</v>
+      </c>
+      <c r="F10" t="n">
+        <v>182615761954.5494</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>179962462977.6937</v>
+      </c>
+      <c r="E11" t="n">
+        <v>178952105214.8109</v>
+      </c>
+      <c r="F11" t="n">
+        <v>178952104170.2944</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>179360164728.3033</v>
+      </c>
+      <c r="E12" t="n">
+        <v>179360164728.3033</v>
+      </c>
+      <c r="F12" t="n">
+        <v>179360165050.4754</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>179360164729.2365</v>
+      </c>
+      <c r="E13" t="n">
+        <v>179360164729.2365</v>
+      </c>
+      <c r="F13" t="n">
+        <v>179360165051.4303</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>223175811424.0905</v>
+      </c>
+      <c r="E14" t="n">
+        <v>209867648125.2209</v>
+      </c>
+      <c r="F14" t="n">
+        <v>199601351085.0942</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MCDA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>179360182150.6298</v>
+      </c>
+      <c r="E15" t="n">
+        <v>179360182610.7973</v>
+      </c>
+      <c r="F15" t="n">
+        <v>179360184926.0942</v>
       </c>
     </row>
   </sheetData>
@@ -1047,23 +1680,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="D1" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -1075,7 +1708,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1089,22 +1722,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14617.51517104317</v>
+        <v>1083.049808530075</v>
       </c>
       <c r="E2" t="n">
-        <v>15803.93802436576</v>
+        <v>1308.70176907129</v>
       </c>
       <c r="F2" t="n">
-        <v>15807.62571916758</v>
+        <v>1334.14691471347</v>
       </c>
       <c r="G2" t="n">
-        <v>15741.58737031025</v>
+        <v>8844.535030510599</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1118,22 +1751,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>250.6680318412663</v>
+        <v>-132.2222222222222</v>
       </c>
       <c r="E3" t="n">
-        <v>250.6680318412668</v>
+        <v>-132.2222222222222</v>
       </c>
       <c r="F3" t="n">
-        <v>154.8013292546502</v>
+        <v>-132.2222222222222</v>
       </c>
       <c r="G3" t="n">
-        <v>154.9014131502542</v>
+        <v>8842.14375273282</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1147,22 +1780,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>154.9014131502542</v>
+        <v>894.3811999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>154.8615804111141</v>
+        <v>781.756951604356</v>
       </c>
       <c r="F4" t="n">
-        <v>154.8615804111141</v>
+        <v>781.756951604356</v>
       </c>
       <c r="G4" t="n">
-        <v>154.8615804111141</v>
+        <v>8704.312852516152</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1176,27 +1809,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>154.8615804111141</v>
+        <v>-132.2222222222222</v>
       </c>
       <c r="E5" t="n">
-        <v>154.9553241732992</v>
+        <v>-132.2222222222222</v>
       </c>
       <c r="F5" t="n">
-        <v>154.9553241732992</v>
+        <v>-132.2222222222222</v>
       </c>
       <c r="G5" t="n">
-        <v>154.9553241732992</v>
+        <v>8842.14375273282</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DIV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1205,45 +1838,256 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>574.3196449255199</v>
+        <v>-132.2222222222222</v>
       </c>
       <c r="E6" t="n">
-        <v>154.8573067931823</v>
+        <v>-132.2222222222222</v>
       </c>
       <c r="F6" t="n">
-        <v>154.8013292546502</v>
+        <v>-132.2222222222222</v>
       </c>
       <c r="G6" t="n">
-        <v>154.8438307022274</v>
+        <v>8842.14375273282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hh_1</t>
+          <t>hh_3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-119.9416572903269</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-124.4126488445111</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-124.4126488445111</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8842.14375273282</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hh_3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>MCDA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>income</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>250.7617757862024</v>
-      </c>
-      <c r="E7" t="n">
-        <v>357.1478797752738</v>
-      </c>
-      <c r="F7" t="n">
-        <v>357.1272812139573</v>
-      </c>
-      <c r="G7" t="n">
-        <v>357.1272812139573</v>
+      <c r="D8" t="n">
+        <v>-132.2222222222211</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-132.2222222222224</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-132.2222222222224</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8840.037463627265</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-6655.300429927167</v>
+      </c>
+      <c r="E9" t="n">
+        <v>39454.57867341413</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30282.34087634909</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>WAT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-11689.14139634341</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-11312.56705610008</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-11058.25440208454</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-262855.6372393807</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-342668.5451114694</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-294545.9594784733</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-10836.98739616887</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-10836.98739616887</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-10836.98739616887</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-10836.98739616887</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-10836.98739616887</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-10836.98739616887</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-8284.90579316585</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-7712.068011913336</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-7258.759507834809</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MCDA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-8001.538532548891</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-13302.65420825591</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-31144.92301055618</v>
       </c>
     </row>
   </sheetData>
@@ -1257,23 +2101,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="D1" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -1285,30 +2129,308 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>hh_3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4342.110153560044</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5136.361936274011</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5248.236405661243</v>
+      </c>
+      <c r="G2" t="n">
+        <v>205490.6856176499</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hh_3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6051.986931699818</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5495.474207206427</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5495.474207206427</v>
+      </c>
+      <c r="G3" t="n">
+        <v>249787.755707938</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hh_3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>93.8415527265015</v>
+      </c>
+      <c r="E4" t="n">
+        <v>71.34773356503564</v>
+      </c>
+      <c r="F4" t="n">
+        <v>71.34773356503564</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40584.0883077423</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>hh_1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.973415985921922</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.973415985921922</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.613216616579978</v>
+      </c>
+      <c r="G5" t="n">
+        <v>100957.2112180278</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hh_1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.817792706402778</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.817792706402778</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.523682110385765</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.994267382259757e-06</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hh_1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8.95861756743324</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.37771792598185</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.535577245897547</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20897.31498642392</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hh_1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MCDA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4838.463460805214</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5647.029999998133</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4317.336340699176</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.079514109437754e-06</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>GM</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>productivity</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>25605.45109315393</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27686.64371976296</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27687.02696109384</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27687.09330005233</v>
+      <c r="D9" t="n">
+        <v>118356.52</v>
+      </c>
+      <c r="E9" t="n">
+        <v>140110.335</v>
+      </c>
+      <c r="F9" t="n">
+        <v>124457.1926955222</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>224052.8862385062</v>
+      </c>
+      <c r="E10" t="n">
+        <v>256153.5264614607</v>
+      </c>
+      <c r="F10" t="n">
+        <v>282077.0204220026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10.4725</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.898764097091317</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hh_2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MCDA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>productivity</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>9189.614651833692</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10895.02772547266</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6966.175617934734</v>
       </c>
     </row>
   </sheetData>
